--- a/artfynd/A 39256-2024 artfynd.xlsx
+++ b/artfynd/A 39256-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120034615</v>
+        <v>120034667</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
+        <v>57463</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593315</v>
+        <v>593340</v>
       </c>
       <c r="R2" t="n">
-        <v>6391488</v>
+        <v>6391420</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120034667</v>
+        <v>120034615</v>
       </c>
       <c r="B3" t="n">
-        <v>57463</v>
+        <v>97907</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,39 +801,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593340</v>
+        <v>593315</v>
       </c>
       <c r="R3" t="n">
-        <v>6391420</v>
+        <v>6391488</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,6 +881,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39256-2024 artfynd.xlsx
+++ b/artfynd/A 39256-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120034667</v>
+        <v>120034615</v>
       </c>
       <c r="B2" t="n">
-        <v>57463</v>
+        <v>97907</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593340</v>
+        <v>593315</v>
       </c>
       <c r="R2" t="n">
-        <v>6391420</v>
+        <v>6391488</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120034615</v>
+        <v>120034667</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
+        <v>57463</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,35 +798,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593315</v>
+        <v>593340</v>
       </c>
       <c r="R3" t="n">
-        <v>6391488</v>
+        <v>6391420</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +882,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39256-2024 artfynd.xlsx
+++ b/artfynd/A 39256-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120034615</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>120034667</v>
       </c>
       <c r="B3" t="n">
-        <v>57463</v>
+        <v>57473</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 39256-2024 artfynd.xlsx
+++ b/artfynd/A 39256-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120034615</v>
+        <v>120034667</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593315</v>
+        <v>593340</v>
       </c>
       <c r="R2" t="n">
-        <v>6391488</v>
+        <v>6391420</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120034667</v>
+        <v>120034615</v>
       </c>
       <c r="B3" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,39 +801,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593340</v>
+        <v>593315</v>
       </c>
       <c r="R3" t="n">
-        <v>6391420</v>
+        <v>6391488</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,6 +881,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39256-2024 artfynd.xlsx
+++ b/artfynd/A 39256-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120034667</v>
+        <v>120034615</v>
       </c>
       <c r="B2" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593340</v>
+        <v>593315</v>
       </c>
       <c r="R2" t="n">
-        <v>6391420</v>
+        <v>6391488</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120034615</v>
+        <v>120034667</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,35 +798,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593315</v>
+        <v>593340</v>
       </c>
       <c r="R3" t="n">
-        <v>6391488</v>
+        <v>6391420</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +882,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
